--- a/output/第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx
+++ b/output/第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx
@@ -1028,7 +1028,7 @@
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>注1）本表の第9期の数値は、第9期計画 第6章第6節（保険料基準額の算出フロー及び所得段階と保険料額）並びに第7節（低所得者支援）の掲載値による。注2）国の標準乗率は介護保険法施行令第38条及び第39条による第9期の標準である。第10期の標準は政令改正により定まるため、告示後に再確認する（09シート No.1）。注3）本表は保険料の水準そのものではなく、段階設定と軽減措置の設計を検証するものである。水準の他団体比較は「保険料と施策評価の他団体比較」01シートによる。</t>
+          <t>注1）本表の第9期の数値は、第9期計画 第6章第6節（保険料基準額の算出フロー及び所得段階と保険料額）並びに第7節（低所得者支援）の掲載値による。注2）国の標準乗率は介護保険法施行令第38条及び第39条による第9期の標準である（施行令の条文は直接確認しておらず、複数の自治体公表資料により確認した）。第10期の標準は政令改正により定まるため、告示後に再確認する（09シート No.1）。注3）本表は保険料の水準そのものではなく、段階設定と軽減措置の設計を検証するものである。水準の他団体比較は「保険料と施策評価の他団体比較」01シートによる。</t>
         </is>
       </c>
     </row>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1">
+    <row r="28" ht="48" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>注1）国標準の乗率は介護保険法施行令第38条・第39条による第9期（令和6年度〜）の標準である。第9期の改正で標準段階が9段階から13段階に多段階化され、高所得層の乗率引上げを財源として第1〜3段階の乗率が引き下げられた。注2）当広域連合の第13〜16段階は、国標準では第13段階（合計所得720万円以上）に一括される。当広域連合はこれを4段階に細分化し、乗率を2.565〜2.595としている。注3）第9段階（320万円以上420万円未満）の乗率1.63が国標準1.70を下回っている点は、低所得者対策として説明しにくい。第8期の9段階制における乗率を引き継いだ可能性があり、経緯の確認を要する（09シート No.2）。注4）年額は百円未満を四捨五入している。</t>
+          <t>注1）国標準の乗率は介護保険法施行令第38条・第39条による第9期（令和6年度〜）の標準である（施行令の条文は直接確認しておらず、複数の自治体公表資料により確認した。レッドチームレビューNo.26）。第9期の改正で標準段階が9段階から13段階に多段階化され、高所得層の乗率引上げを財源として第1〜3段階の乗率が引き下げられた。注2）当広域連合の第13〜16段階は、国標準では第13段階（合計所得720万円以上）に一括される。当広域連合はこれを4段階に細分化し、乗率を2.565〜2.595としている。注3）第9段階（320万円以上420万円未満）の乗率1.63が国標準1.70を下回っている点は、低所得者対策として説明しにくい。第8期の9段階制における乗率を引き継いだ可能性があり、経緯の確認を要する（09シート No.2）。注4）年額は百円未満を四捨五入している。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx
+++ b/output/第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx
@@ -2890,7 +2890,7 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>注1）国標準の乗率は介護保険法施行令第38条・第39条による第9期（令和6年度〜）の標準である（施行令の条文は直接確認しておらず、複数の自治体公表資料により確認した。レッドチームレビューNo.26）。第9期の改正で標準段階が9段階から13段階に多段階化され、高所得層の乗率引上げを財源として第1〜3段階の乗率が引き下げられた。注2）当広域連合の第13〜16段階は、国標準では第13段階（合計所得720万円以上）に一括される。当広域連合はこれを4段階に細分化し、乗率を2.565〜2.595としている。注3）第9段階（320万円以上420万円未満）の乗率1.63が国標準1.70を下回っている点は、低所得者対策として説明しにくい。第8期の9段階制における乗率を引き継いだ可能性があり、経緯の確認を要する（09シート No.2）。注4）年額は百円未満を四捨五入している。</t>
+          <t>注1）国標準の乗率は介護保険法施行令第38条・第39条による第9期（令和6年度〜）の標準である（施行令の条文は直接確認しておらず、複数の自治体公表資料により確認した。自己点検記録No.26）。第9期の改正で標準段階が9段階から13段階に多段階化され、高所得層の乗率引上げを財源として第1〜3段階の乗率が引き下げられた。注2）当広域連合の第13〜16段階は、国標準では第13段階（合計所得720万円以上）に一括される。当広域連合はこれを4段階に細分化し、乗率を2.565〜2.595としている。注3）第9段階（320万円以上420万円未満）の乗率1.63が国標準1.70を下回っている点は、低所得者対策として説明しにくい。第8期の9段階制における乗率を引き継いだ可能性があり、経緯の確認を要する（09シート No.2）。注4）年額は百円未満を四捨五入している。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx
+++ b/output/第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx
@@ -2890,7 +2890,7 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>注1）国標準の乗率は介護保険法施行令第38条・第39条による第9期（令和6年度〜）の標準である（施行令の条文は直接確認しておらず、複数の自治体公表資料により確認した。自己点検記録No.26）。第9期の改正で標準段階が9段階から13段階に多段階化され、高所得層の乗率引上げを財源として第1〜3段階の乗率が引き下げられた。注2）当広域連合の第13〜16段階は、国標準では第13段階（合計所得720万円以上）に一括される。当広域連合はこれを4段階に細分化し、乗率を2.565〜2.595としている。注3）第9段階（320万円以上420万円未満）の乗率1.63が国標準1.70を下回っている点は、低所得者対策として説明しにくい。第8期の9段階制における乗率を引き継いだ可能性があり、経緯の確認を要する（09シート No.2）。注4）年額は百円未満を四捨五入している。</t>
+          <t>注1）国標準の乗率は介護保険法施行令第38条・第39条による第9期（令和6年度〜）の標準である（施行令の条文は直接確認しておらず、複数の自治体公表資料により確認した。受託者の自己点検）。第9期の改正で標準段階が9段階から13段階に多段階化され、高所得層の乗率引上げを財源として第1〜3段階の乗率が引き下げられた。注2）当広域連合の第13〜16段階は、国標準では第13段階（合計所得720万円以上）に一括される。当広域連合はこれを4段階に細分化し、乗率を2.565〜2.595としている。注3）第9段階（320万円以上420万円未満）の乗率1.63が国標準1.70を下回っている点は、低所得者対策として説明しにくい。第8期の9段階制における乗率を引き継いだ可能性があり、経緯の確認を要する（09シート No.2）。注4）年額は百円未満を四捨五入している。</t>
         </is>
       </c>
     </row>
